--- a/src/test/resources/UserExcelSample.xlsx
+++ b/src/test/resources/UserExcelSample.xlsx
@@ -308,10 +308,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1048576"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="8.73046875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -319,7 +319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -327,7 +327,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -335,7 +335,6 @@
         <v>32</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
